--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu475000_stage1b_rep3.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu475000_stage1b_rep3.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130425</t>
+          <t>64360</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>120252</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>118787</t>
+          <t>62896</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>122347</t>
+          <t>59521</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>115735</t>
+          <t>56283</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>108057</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>101487</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>99626</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>96630</t>
+          <t>46718</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>61623</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>118657</t>
+          <t>57104</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>116043</t>
+          <t>59008</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>112355</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>97813</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>78325</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
